--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N11_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N11_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>87.3683139076132</v>
+        <v>14.19735100998714</v>
       </c>
       <c r="D2" t="n">
-        <v>88.01989767533775</v>
+        <v>14.30323337224238</v>
       </c>
       <c r="E2" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F2" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>76.24172382615566</v>
+        <v>12.3892801217503</v>
       </c>
       <c r="D3" t="n">
-        <v>76.82989100662373</v>
+        <v>12.48485728857636</v>
       </c>
       <c r="E3" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F3" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>83.79176596414595</v>
+        <v>13.61616196917372</v>
       </c>
       <c r="D4" t="n">
-        <v>84.54063808809737</v>
+        <v>13.73785368931582</v>
       </c>
       <c r="E4" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F4" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>40.2410345502946</v>
+        <v>6.539168114422873</v>
       </c>
       <c r="D5" t="n">
-        <v>80.84351885788784</v>
+        <v>13.13707181440678</v>
       </c>
       <c r="E5" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F5" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.33442369448792</v>
+        <v>5.741843850354287</v>
       </c>
       <c r="D6" t="n">
-        <v>35.79129576409267</v>
+        <v>5.81608556166506</v>
       </c>
       <c r="E6" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F6" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.13434549867078</v>
+        <v>6.521831143534002</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28285515490639</v>
+        <v>6.383463962672289</v>
       </c>
       <c r="E7" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F7" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.13653123941016</v>
+        <v>3.109686326404151</v>
       </c>
       <c r="D8" t="n">
-        <v>18.28869179184379</v>
+        <v>2.971912416174616</v>
       </c>
       <c r="E8" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F8" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>14.58489694977861</v>
+        <v>2.370045754339025</v>
       </c>
       <c r="D9" t="n">
-        <v>14.02289410607422</v>
+        <v>2.278720292237061</v>
       </c>
       <c r="E9" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F9" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.6222656140992</v>
+        <v>1.56361816229112</v>
       </c>
       <c r="D10" t="n">
-        <v>10.1998970864213</v>
+        <v>1.657483276543461</v>
       </c>
       <c r="E10" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F10" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>52.92733060140439</v>
+        <v>8.600691222728214</v>
       </c>
       <c r="D11" t="n">
-        <v>52.22781473776032</v>
+        <v>8.487019894886052</v>
       </c>
       <c r="E11" t="n">
-        <v>27.04678713157888</v>
+        <v>4.395102908881569</v>
       </c>
       <c r="F11" t="n">
-        <v>29.18124195099561</v>
+        <v>4.741951817036787</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
